--- a/data/H131_20260618_14.xlsx
+++ b/data/H131_20260618_14.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>595.0</v>
+        <v>601.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,10 +610,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>595.0</v>
+        <v>601.0</v>
       </c>
       <c r="O4" s="2">
-        <v>264.0</v>
+        <v>270.0</v>
       </c>
       <c r="P4" s="2">
         <v>331.0</v>
@@ -669,7 +669,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -681,13 +681,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="O5" s="2">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="P5" s="2">
-        <v>244.0</v>
+        <v>248.0</v>
       </c>
       <c r="Q5" s="2">
         <v>1.0</v>
@@ -740,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>671.0</v>
+        <v>674.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -752,10 +752,10 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>671.0</v>
+        <v>674.0</v>
       </c>
       <c r="O6" s="2">
-        <v>317.0</v>
+        <v>320.0</v>
       </c>
       <c r="P6" s="2">
         <v>354.0</v>
@@ -953,7 +953,7 @@
         <v>730.0</v>
       </c>
       <c r="J9" s="2">
-        <v>419.0</v>
+        <v>428.0</v>
       </c>
       <c r="K9" s="2">
         <v>1.0</v>
@@ -965,13 +965,13 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="2">
-        <v>419.0</v>
+        <v>428.0</v>
       </c>
       <c r="O9" s="2">
-        <v>217.0</v>
+        <v>221.0</v>
       </c>
       <c r="P9" s="2">
-        <v>202.0</v>
+        <v>207.0</v>
       </c>
       <c r="Q9" s="2">
         <v>0.0</v>
@@ -1166,7 +1166,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>738.0</v>
+        <v>741.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1178,10 +1178,10 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>738.0</v>
+        <v>741.0</v>
       </c>
       <c r="O12" s="2">
-        <v>423.0</v>
+        <v>426.0</v>
       </c>
       <c r="P12" s="2">
         <v>315.0</v>
@@ -1237,7 +1237,7 @@
         <v>1245.0</v>
       </c>
       <c r="J13" s="2">
-        <v>1004.0</v>
+        <v>1026.0</v>
       </c>
       <c r="K13" s="2">
         <v>1.0</v>
@@ -1249,22 +1249,22 @@
         <v>0.0</v>
       </c>
       <c r="N13" s="2">
-        <v>1004.0</v>
+        <v>1026.0</v>
       </c>
       <c r="O13" s="2">
-        <v>523.0</v>
+        <v>535.0</v>
       </c>
       <c r="P13" s="2">
-        <v>481.0</v>
+        <v>491.0</v>
       </c>
       <c r="Q13" s="2">
         <v>0.0</v>
       </c>
       <c r="R13" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="S13" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="T13" s="2">
         <v>4.0</v>
@@ -1276,7 +1276,7 @@
         <v>0.0</v>
       </c>
       <c r="W13" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="14">
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>669.0</v>
+        <v>728.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,13 +1320,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>669.0</v>
+        <v>728.0</v>
       </c>
       <c r="O14" s="2">
-        <v>282.0</v>
+        <v>339.0</v>
       </c>
       <c r="P14" s="2">
-        <v>387.0</v>
+        <v>389.0</v>
       </c>
       <c r="Q14" s="2">
         <v>0.0</v>
@@ -1335,7 +1335,7 @@
         <v>33.0</v>
       </c>
       <c r="S14" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="T14" s="2">
         <v>1.0</v>
@@ -1347,7 +1347,7 @@
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>449.0</v>
+        <v>481.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>449.0</v>
+        <v>481.0</v>
       </c>
       <c r="O15" s="2">
-        <v>198.0</v>
+        <v>222.0</v>
       </c>
       <c r="P15" s="2">
-        <v>251.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>609.0</v>
+        <v>674.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,22 +1675,22 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>609.0</v>
+        <v>674.0</v>
       </c>
       <c r="O19" s="2">
-        <v>319.0</v>
+        <v>352.0</v>
       </c>
       <c r="P19" s="2">
-        <v>290.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
       </c>
       <c r="R19" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S19" s="2">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="T19" s="2">
         <v>3.0</v>
@@ -1702,7 +1702,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>28.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1734,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" s="2">
-        <v>847.0</v>
+        <v>915.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1746,22 +1746,22 @@
         <v>1.0</v>
       </c>
       <c r="N20" s="2">
-        <v>846.0</v>
+        <v>914.0</v>
       </c>
       <c r="O20" s="2">
-        <v>466.0</v>
+        <v>510.0</v>
       </c>
       <c r="P20" s="2">
-        <v>381.0</v>
+        <v>405.0</v>
       </c>
       <c r="Q20" s="2">
         <v>0.0</v>
       </c>
       <c r="R20" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="S20" s="2">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="T20" s="2">
         <v>5.0</v>
@@ -1773,7 +1773,7 @@
         <v>0.0</v>
       </c>
       <c r="W20" s="2">
-        <v>35.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1900,7 +1900,7 @@
         <v>0.0</v>
       </c>
       <c r="R22" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="S22" s="2">
         <v>0.0</v>
@@ -1915,7 +1915,7 @@
         <v>0.0</v>
       </c>
       <c r="W22" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>570.0</v>
+        <v>687.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>570.0</v>
+        <v>687.0</v>
       </c>
       <c r="O24" s="2">
-        <v>323.0</v>
+        <v>396.0</v>
       </c>
       <c r="P24" s="2">
-        <v>232.0</v>
+        <v>276.0</v>
       </c>
       <c r="Q24" s="2">
         <v>15.0</v>
@@ -2444,7 +2444,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>225.0</v>
+        <v>229.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2456,10 +2456,10 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <v>225.0</v>
+        <v>229.0</v>
       </c>
       <c r="O30" s="2">
-        <v>128.0</v>
+        <v>132.0</v>
       </c>
       <c r="P30" s="2">
         <v>78.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>635.0</v>
+        <v>640.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,13 +2527,13 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>635.0</v>
+        <v>640.0</v>
       </c>
       <c r="O31" s="2">
-        <v>318.0</v>
+        <v>320.0</v>
       </c>
       <c r="P31" s="2">
-        <v>312.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q31" s="2">
         <v>5.0</v>
@@ -2586,7 +2586,7 @@
         <v>1143.0</v>
       </c>
       <c r="J32" s="2">
-        <v>669.0</v>
+        <v>682.0</v>
       </c>
       <c r="K32" s="2">
         <v>1.0</v>
@@ -2598,13 +2598,13 @@
         <v>0.0</v>
       </c>
       <c r="N32" s="2">
-        <v>669.0</v>
+        <v>682.0</v>
       </c>
       <c r="O32" s="2">
-        <v>318.0</v>
+        <v>324.0</v>
       </c>
       <c r="P32" s="2">
-        <v>334.0</v>
+        <v>341.0</v>
       </c>
       <c r="Q32" s="2">
         <v>17.0</v>
@@ -2657,7 +2657,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" s="2">
-        <v>304.0</v>
+        <v>306.0</v>
       </c>
       <c r="K33" s="2">
         <v>1.0</v>
@@ -2669,22 +2669,22 @@
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <v>304.0</v>
+        <v>306.0</v>
       </c>
       <c r="O33" s="2">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="P33" s="2">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="Q33" s="2">
         <v>0.0</v>
       </c>
       <c r="R33" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="S33" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="T33" s="2">
         <v>0.0</v>
@@ -2696,7 +2696,7 @@
         <v>0.0</v>
       </c>
       <c r="W33" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -2728,7 +2728,7 @@
         <v>647.0</v>
       </c>
       <c r="J34" s="2">
-        <v>581.0</v>
+        <v>604.0</v>
       </c>
       <c r="K34" s="2">
         <v>1.0</v>
@@ -2740,13 +2740,13 @@
         <v>0.0</v>
       </c>
       <c r="N34" s="2">
-        <v>581.0</v>
+        <v>604.0</v>
       </c>
       <c r="O34" s="2">
-        <v>319.0</v>
+        <v>337.0</v>
       </c>
       <c r="P34" s="2">
-        <v>262.0</v>
+        <v>267.0</v>
       </c>
       <c r="Q34" s="2">
         <v>0.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>359.0</v>
+        <v>366.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,13 +2811,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>359.0</v>
+        <v>366.0</v>
       </c>
       <c r="O35" s="2">
-        <v>183.0</v>
+        <v>186.0</v>
       </c>
       <c r="P35" s="2">
-        <v>167.0</v>
+        <v>171.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>465.0</v>
+        <v>487.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,13 +2882,13 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>465.0</v>
+        <v>487.0</v>
       </c>
       <c r="O36" s="2">
-        <v>195.0</v>
+        <v>207.0</v>
       </c>
       <c r="P36" s="2">
-        <v>270.0</v>
+        <v>280.0</v>
       </c>
       <c r="Q36" s="2">
         <v>0.0</v>
@@ -2941,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>434.0</v>
+        <v>439.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2953,13 +2953,13 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>434.0</v>
+        <v>439.0</v>
       </c>
       <c r="O37" s="2">
-        <v>226.0</v>
+        <v>229.0</v>
       </c>
       <c r="P37" s="2">
-        <v>204.0</v>
+        <v>206.0</v>
       </c>
       <c r="Q37" s="2">
         <v>4.0</v>
@@ -3083,7 +3083,7 @@
         <v>585.0</v>
       </c>
       <c r="J39" s="2">
-        <v>400.0</v>
+        <v>407.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,19 +3095,19 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>400.0</v>
+        <v>407.0</v>
       </c>
       <c r="O39" s="2">
-        <v>199.0</v>
+        <v>202.0</v>
       </c>
       <c r="P39" s="2">
-        <v>201.0</v>
+        <v>205.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
       </c>
       <c r="R39" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="S39" s="2">
         <v>7.0</v>
@@ -3122,7 +3122,7 @@
         <v>0.0</v>
       </c>
       <c r="W39" s="2">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>422.0</v>
+        <v>469.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,22 +3308,22 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>422.0</v>
+        <v>469.0</v>
       </c>
       <c r="O42" s="2">
-        <v>267.0</v>
+        <v>302.0</v>
       </c>
       <c r="P42" s="2">
-        <v>155.0</v>
+        <v>167.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
       </c>
       <c r="R42" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="S42" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="T42" s="2">
         <v>0.0</v>
@@ -3335,7 +3335,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3367,7 +3367,7 @@
         <v>1022.0</v>
       </c>
       <c r="J43" s="2">
-        <v>671.0</v>
+        <v>705.0</v>
       </c>
       <c r="K43" s="2">
         <v>1.0</v>
@@ -3379,13 +3379,13 @@
         <v>0.0</v>
       </c>
       <c r="N43" s="2">
-        <v>671.0</v>
+        <v>705.0</v>
       </c>
       <c r="O43" s="2">
-        <v>322.0</v>
+        <v>342.0</v>
       </c>
       <c r="P43" s="2">
-        <v>349.0</v>
+        <v>363.0</v>
       </c>
       <c r="Q43" s="2">
         <v>0.0</v>
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1003.0</v>
+        <v>1027.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,34 +3521,34 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1002.0</v>
+        <v>1026.0</v>
       </c>
       <c r="O45" s="2">
-        <v>473.0</v>
+        <v>481.0</v>
       </c>
       <c r="P45" s="2">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>15.0</v>
+        <v>30.0</v>
       </c>
       <c r="R45" s="2">
         <v>48.0</v>
       </c>
       <c r="S45" s="2">
-        <v>21.0</v>
+        <v>31.0</v>
       </c>
       <c r="T45" s="2">
         <v>0.0</v>
       </c>
       <c r="U45" s="2">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="V45" s="2">
         <v>0.0</v>
       </c>
       <c r="W45" s="2">
-        <v>77.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3651,7 +3651,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" s="2">
-        <v>721.0</v>
+        <v>726.0</v>
       </c>
       <c r="K47" s="2">
         <v>1.0</v>
@@ -3663,13 +3663,13 @@
         <v>0.0</v>
       </c>
       <c r="N47" s="2">
-        <v>721.0</v>
+        <v>726.0</v>
       </c>
       <c r="O47" s="2">
-        <v>393.0</v>
+        <v>396.0</v>
       </c>
       <c r="P47" s="2">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="Q47" s="2">
         <v>1.0</v>
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>876.0</v>
+        <v>892.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,19 +3734,19 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>876.0</v>
+        <v>892.0</v>
       </c>
       <c r="O48" s="2">
-        <v>501.0</v>
+        <v>508.0</v>
       </c>
       <c r="P48" s="2">
-        <v>375.0</v>
+        <v>384.0</v>
       </c>
       <c r="Q48" s="2">
         <v>0.0</v>
       </c>
       <c r="R48" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S48" s="2">
         <v>0.0</v>
@@ -3761,7 +3761,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>905.0</v>
+        <v>932.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,13 +3805,13 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>905.0</v>
+        <v>932.0</v>
       </c>
       <c r="O49" s="2">
-        <v>471.0</v>
+        <v>494.0</v>
       </c>
       <c r="P49" s="2">
-        <v>434.0</v>
+        <v>438.0</v>
       </c>
       <c r="Q49" s="2">
         <v>0.0</v>
@@ -3864,7 +3864,7 @@
         <v>582.0</v>
       </c>
       <c r="J50" s="2">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="K50" s="2">
         <v>1.0</v>
@@ -3876,19 +3876,19 @@
         <v>3.0</v>
       </c>
       <c r="N50" s="2">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="O50" s="2">
         <v>216.0</v>
       </c>
       <c r="P50" s="2">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="Q50" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="R50" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="S50" s="2">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>0.0</v>
       </c>
       <c r="W50" s="2">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -4148,7 +4148,7 @@
         <v>778.0</v>
       </c>
       <c r="J54" s="2">
-        <v>555.0</v>
+        <v>571.0</v>
       </c>
       <c r="K54" s="2">
         <v>1.0</v>
@@ -4160,13 +4160,13 @@
         <v>0.0</v>
       </c>
       <c r="N54" s="2">
-        <v>555.0</v>
+        <v>571.0</v>
       </c>
       <c r="O54" s="2">
-        <v>293.0</v>
+        <v>301.0</v>
       </c>
       <c r="P54" s="2">
-        <v>262.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q54" s="2">
         <v>0.0</v>
@@ -4290,7 +4290,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>521.0</v>
+        <v>539.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4302,13 +4302,13 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>521.0</v>
+        <v>539.0</v>
       </c>
       <c r="O56" s="2">
-        <v>236.0</v>
+        <v>253.0</v>
       </c>
       <c r="P56" s="2">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="Q56" s="2">
         <v>0.0</v>
@@ -4361,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="O57" s="2">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4432,7 +4432,7 @@
         <v>1059.0</v>
       </c>
       <c r="J58" s="2">
-        <v>649.0</v>
+        <v>699.0</v>
       </c>
       <c r="K58" s="2">
         <v>1.0</v>
@@ -4444,13 +4444,13 @@
         <v>0.0</v>
       </c>
       <c r="N58" s="2">
-        <v>649.0</v>
+        <v>699.0</v>
       </c>
       <c r="O58" s="2">
-        <v>302.0</v>
+        <v>333.0</v>
       </c>
       <c r="P58" s="2">
-        <v>347.0</v>
+        <v>366.0</v>
       </c>
       <c r="Q58" s="2">
         <v>0.0</v>
@@ -4503,7 +4503,7 @@
         <v>909.0</v>
       </c>
       <c r="J59" s="2">
-        <v>574.0</v>
+        <v>589.0</v>
       </c>
       <c r="K59" s="2">
         <v>1.0</v>
@@ -4515,13 +4515,13 @@
         <v>0.0</v>
       </c>
       <c r="N59" s="2">
-        <v>574.0</v>
+        <v>589.0</v>
       </c>
       <c r="O59" s="2">
-        <v>272.0</v>
+        <v>281.0</v>
       </c>
       <c r="P59" s="2">
-        <v>302.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q59" s="2">
         <v>0.0</v>
@@ -4574,7 +4574,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>598.0</v>
+        <v>601.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4586,19 +4586,19 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>598.0</v>
+        <v>601.0</v>
       </c>
       <c r="O60" s="2">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
       <c r="P60" s="2">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q60" s="2">
         <v>0.0</v>
       </c>
       <c r="R60" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S60" s="2">
         <v>0.0</v>
@@ -4613,7 +4613,7 @@
         <v>0.0</v>
       </c>
       <c r="W60" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -4669,10 +4669,10 @@
         <v>0.0</v>
       </c>
       <c r="R61" s="2">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
       <c r="S61" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T61" s="2">
         <v>0.0</v>
@@ -4684,7 +4684,7 @@
         <v>0.0</v>
       </c>
       <c r="W61" s="2">
-        <v>0.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -4740,7 +4740,7 @@
         <v>1.0</v>
       </c>
       <c r="R62" s="2">
-        <v>20.0</v>
+        <v>32.0</v>
       </c>
       <c r="S62" s="2">
         <v>0.0</v>
@@ -4755,7 +4755,7 @@
         <v>0.0</v>
       </c>
       <c r="W62" s="2">
-        <v>20.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -4787,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>705.0</v>
+        <v>724.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4799,10 +4799,10 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>705.0</v>
+        <v>724.0</v>
       </c>
       <c r="O63" s="2">
-        <v>357.0</v>
+        <v>376.0</v>
       </c>
       <c r="P63" s="2">
         <v>348.0</v>
@@ -5213,22 +5213,22 @@
         <v>1122.0</v>
       </c>
       <c r="J69" s="2">
+        <v>958.0</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="L69" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="M69" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N69" s="2">
         <v>957.0</v>
       </c>
-      <c r="K69" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="L69" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="M69" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="N69" s="2">
-        <v>956.0</v>
-      </c>
       <c r="O69" s="2">
-        <v>485.0</v>
+        <v>486.0</v>
       </c>
       <c r="P69" s="2">
         <v>472.0</v>
@@ -5284,7 +5284,7 @@
         <v>1151.0</v>
       </c>
       <c r="J70" s="2">
-        <v>1005.0</v>
+        <v>1020.0</v>
       </c>
       <c r="K70" s="2">
         <v>1.0</v>
@@ -5296,13 +5296,13 @@
         <v>0.0</v>
       </c>
       <c r="N70" s="2">
-        <v>1005.0</v>
+        <v>1020.0</v>
       </c>
       <c r="O70" s="2">
-        <v>625.0</v>
+        <v>637.0</v>
       </c>
       <c r="P70" s="2">
-        <v>371.0</v>
+        <v>374.0</v>
       </c>
       <c r="Q70" s="2">
         <v>9.0</v>
@@ -5426,7 +5426,7 @@
         <v>1141.0</v>
       </c>
       <c r="J72" s="2">
-        <v>1036.0</v>
+        <v>1050.0</v>
       </c>
       <c r="K72" s="2">
         <v>1.0</v>
@@ -5438,34 +5438,34 @@
         <v>0.0</v>
       </c>
       <c r="N72" s="2">
-        <v>1036.0</v>
+        <v>1050.0</v>
       </c>
       <c r="O72" s="2">
-        <v>636.0</v>
+        <v>649.0</v>
       </c>
       <c r="P72" s="2">
-        <v>392.0</v>
+        <v>393.0</v>
       </c>
       <c r="Q72" s="2">
         <v>8.0</v>
       </c>
       <c r="R72" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S72" s="2">
         <v>11.0</v>
       </c>
       <c r="T72" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="U72" s="2">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="V72" s="2">
         <v>0.0</v>
       </c>
       <c r="W72" s="2">
-        <v>57.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
@@ -5639,7 +5639,7 @@
         <v>877.0</v>
       </c>
       <c r="J75" s="2">
-        <v>801.0</v>
+        <v>805.0</v>
       </c>
       <c r="K75" s="2">
         <v>1.0</v>
@@ -5651,16 +5651,16 @@
         <v>0.0</v>
       </c>
       <c r="N75" s="2">
-        <v>801.0</v>
+        <v>805.0</v>
       </c>
       <c r="O75" s="2">
-        <v>416.0</v>
+        <v>418.0</v>
       </c>
       <c r="P75" s="2">
         <v>377.0</v>
       </c>
       <c r="Q75" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="R75" s="2">
         <v>4.0</v>
@@ -5781,7 +5781,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>411.0</v>
+        <v>427.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5793,16 +5793,16 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>411.0</v>
+        <v>427.0</v>
       </c>
       <c r="O77" s="2">
         <v>58.0</v>
       </c>
       <c r="P77" s="2">
-        <v>301.0</v>
+        <v>303.0</v>
       </c>
       <c r="Q77" s="2">
-        <v>52.0</v>
+        <v>66.0</v>
       </c>
       <c r="R77" s="2">
         <v>0.0</v>
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
       <c r="O78" s="2">
         <v>165.0</v>
       </c>
       <c r="P78" s="2">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5923,7 +5923,7 @@
         <v>786.0</v>
       </c>
       <c r="J79" s="2">
-        <v>316.0</v>
+        <v>344.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5935,13 +5935,13 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>316.0</v>
+        <v>344.0</v>
       </c>
       <c r="O79" s="2">
-        <v>104.0</v>
+        <v>130.0</v>
       </c>
       <c r="P79" s="2">
-        <v>212.0</v>
+        <v>214.0</v>
       </c>
       <c r="Q79" s="2">
         <v>0.0</v>
@@ -6207,7 +6207,7 @@
         <v>1127.0</v>
       </c>
       <c r="J83" s="2">
-        <v>800.0</v>
+        <v>802.0</v>
       </c>
       <c r="K83" s="2">
         <v>1.0</v>
@@ -6219,10 +6219,10 @@
         <v>0.0</v>
       </c>
       <c r="N83" s="2">
-        <v>800.0</v>
+        <v>802.0</v>
       </c>
       <c r="O83" s="2">
-        <v>385.0</v>
+        <v>387.0</v>
       </c>
       <c r="P83" s="2">
         <v>415.0</v>
@@ -6420,7 +6420,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>884.0</v>
+        <v>905.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6432,13 +6432,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>884.0</v>
+        <v>905.0</v>
       </c>
       <c r="O86" s="2">
-        <v>417.0</v>
+        <v>428.0</v>
       </c>
       <c r="P86" s="2">
-        <v>467.0</v>
+        <v>477.0</v>
       </c>
       <c r="Q86" s="2">
         <v>0.0</v>
@@ -6491,7 +6491,7 @@
         <v>735.0</v>
       </c>
       <c r="J87" s="2">
-        <v>648.0</v>
+        <v>662.0</v>
       </c>
       <c r="K87" s="2">
         <v>1.0</v>
@@ -6503,13 +6503,13 @@
         <v>0.0</v>
       </c>
       <c r="N87" s="2">
-        <v>648.0</v>
+        <v>662.0</v>
       </c>
       <c r="O87" s="2">
+        <v>334.0</v>
+      </c>
+      <c r="P87" s="2">
         <v>328.0</v>
-      </c>
-      <c r="P87" s="2">
-        <v>320.0</v>
       </c>
       <c r="Q87" s="2">
         <v>0.0</v>
@@ -6518,19 +6518,19 @@
         <v>21.0</v>
       </c>
       <c r="S87" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="T87" s="2">
         <v>8.0</v>
       </c>
       <c r="U87" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="V87" s="2">
         <v>0.0</v>
       </c>
       <c r="W87" s="2">
-        <v>35.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>455.0</v>
+        <v>466.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,10 +6645,10 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>455.0</v>
+        <v>466.0</v>
       </c>
       <c r="O89" s="2">
-        <v>189.0</v>
+        <v>200.0</v>
       </c>
       <c r="P89" s="2">
         <v>266.0</v>
@@ -6657,7 +6657,7 @@
         <v>0.0</v>
       </c>
       <c r="R89" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="S89" s="2">
         <v>10.0</v>
@@ -6672,7 +6672,7 @@
         <v>0.0</v>
       </c>
       <c r="W89" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -6704,7 +6704,7 @@
         <v>744.0</v>
       </c>
       <c r="J90" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="K90" s="2">
         <v>1.0</v>
@@ -6716,13 +6716,13 @@
         <v>0.0</v>
       </c>
       <c r="N90" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="O90" s="2">
         <v>336.0</v>
       </c>
       <c r="P90" s="2">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="Q90" s="2">
         <v>2.0</v>
@@ -6775,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>631.0</v>
+        <v>638.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6787,19 +6787,19 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>631.0</v>
+        <v>638.0</v>
       </c>
       <c r="O91" s="2">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="P91" s="2">
-        <v>313.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>192.0</v>
+        <v>195.0</v>
       </c>
       <c r="R91" s="2">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="S91" s="2">
         <v>22.0</v>
@@ -6808,13 +6808,13 @@
         <v>1.0</v>
       </c>
       <c r="U91" s="2">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>92.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6846,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>612.0</v>
+        <v>632.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6858,22 +6858,22 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>612.0</v>
+        <v>632.0</v>
       </c>
       <c r="O92" s="2">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="P92" s="2">
-        <v>272.0</v>
+        <v>283.0</v>
       </c>
       <c r="Q92" s="2">
-        <v>85.0</v>
+        <v>89.0</v>
       </c>
       <c r="R92" s="2">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="S92" s="2">
-        <v>72.0</v>
+        <v>79.0</v>
       </c>
       <c r="T92" s="2">
         <v>10.0</v>
@@ -6885,7 +6885,7 @@
         <v>2.0</v>
       </c>
       <c r="W92" s="2">
-        <v>129.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>720.0</v>
+        <v>732.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,13 +6929,13 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>720.0</v>
+        <v>732.0</v>
       </c>
       <c r="O93" s="2">
-        <v>398.0</v>
+        <v>407.0</v>
       </c>
       <c r="P93" s="2">
-        <v>321.0</v>
+        <v>324.0</v>
       </c>
       <c r="Q93" s="2">
         <v>1.0</v>
@@ -6988,7 +6988,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>540.0</v>
+        <v>564.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -7000,13 +7000,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>540.0</v>
+        <v>564.0</v>
       </c>
       <c r="O94" s="2">
-        <v>237.0</v>
+        <v>248.0</v>
       </c>
       <c r="P94" s="2">
-        <v>303.0</v>
+        <v>316.0</v>
       </c>
       <c r="Q94" s="2">
         <v>0.0</v>
@@ -7059,7 +7059,7 @@
         <v>1421.0</v>
       </c>
       <c r="J95" s="2">
-        <v>1246.0</v>
+        <v>1258.0</v>
       </c>
       <c r="K95" s="2">
         <v>1.0</v>
@@ -7071,13 +7071,13 @@
         <v>0.0</v>
       </c>
       <c r="N95" s="2">
-        <v>1246.0</v>
+        <v>1258.0</v>
       </c>
       <c r="O95" s="2">
-        <v>601.0</v>
+        <v>612.0</v>
       </c>
       <c r="P95" s="2">
-        <v>645.0</v>
+        <v>646.0</v>
       </c>
       <c r="Q95" s="2">
         <v>0.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>348.0</v>
+        <v>369.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,19 +7284,19 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>348.0</v>
+        <v>369.0</v>
       </c>
       <c r="O98" s="2">
-        <v>142.0</v>
+        <v>151.0</v>
       </c>
       <c r="P98" s="2">
-        <v>206.0</v>
+        <v>218.0</v>
       </c>
       <c r="Q98" s="2">
         <v>0.0</v>
       </c>
       <c r="R98" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="S98" s="2">
         <v>0.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7343,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>688.0</v>
+        <v>696.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,13 +7355,13 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>688.0</v>
+        <v>696.0</v>
       </c>
       <c r="O99" s="2">
-        <v>345.0</v>
+        <v>350.0</v>
       </c>
       <c r="P99" s="2">
-        <v>343.0</v>
+        <v>346.0</v>
       </c>
       <c r="Q99" s="2">
         <v>0.0</v>
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>937.0</v>
+        <v>947.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,13 +7426,13 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>937.0</v>
+        <v>947.0</v>
       </c>
       <c r="O100" s="2">
-        <v>398.0</v>
+        <v>401.0</v>
       </c>
       <c r="P100" s="2">
-        <v>539.0</v>
+        <v>546.0</v>
       </c>
       <c r="Q100" s="2">
         <v>0.0</v>
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>420.0</v>
+        <v>426.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,13 +7639,13 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>420.0</v>
+        <v>426.0</v>
       </c>
       <c r="O103" s="2">
-        <v>210.0</v>
+        <v>215.0</v>
       </c>
       <c r="P103" s="2">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q103" s="2">
         <v>0.0</v>
@@ -7769,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>685.0</v>
+        <v>695.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7781,13 +7781,13 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>685.0</v>
+        <v>695.0</v>
       </c>
       <c r="O105" s="2">
-        <v>328.0</v>
+        <v>335.0</v>
       </c>
       <c r="P105" s="2">
-        <v>357.0</v>
+        <v>360.0</v>
       </c>
       <c r="Q105" s="2">
         <v>0.0</v>
@@ -7840,7 +7840,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" s="2">
-        <v>715.0</v>
+        <v>759.0</v>
       </c>
       <c r="K106" s="2">
         <v>1.0</v>
@@ -7852,13 +7852,13 @@
         <v>0.0</v>
       </c>
       <c r="N106" s="2">
-        <v>715.0</v>
+        <v>759.0</v>
       </c>
       <c r="O106" s="2">
-        <v>302.0</v>
+        <v>327.0</v>
       </c>
       <c r="P106" s="2">
-        <v>403.0</v>
+        <v>422.0</v>
       </c>
       <c r="Q106" s="2">
         <v>10.0</v>
@@ -7911,7 +7911,7 @@
         <v>1053.0</v>
       </c>
       <c r="J107" s="2">
-        <v>429.0</v>
+        <v>525.0</v>
       </c>
       <c r="K107" s="2">
         <v>1.0</v>
@@ -7923,13 +7923,13 @@
         <v>3.0</v>
       </c>
       <c r="N107" s="2">
-        <v>426.0</v>
+        <v>522.0</v>
       </c>
       <c r="O107" s="2">
-        <v>182.0</v>
+        <v>260.0</v>
       </c>
       <c r="P107" s="2">
-        <v>247.0</v>
+        <v>265.0</v>
       </c>
       <c r="Q107" s="2">
         <v>0.0</v>
@@ -7982,7 +7982,7 @@
         <v>950.0</v>
       </c>
       <c r="J108" s="2">
-        <v>498.0</v>
+        <v>499.0</v>
       </c>
       <c r="K108" s="2">
         <v>1.0</v>
@@ -7991,13 +7991,13 @@
         <v>1.0</v>
       </c>
       <c r="M108" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="N108" s="2">
         <v>498.0</v>
       </c>
       <c r="O108" s="2">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="P108" s="2">
         <v>217.0</v>
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>391.0</v>
+        <v>395.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,13 +8136,13 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>391.0</v>
+        <v>395.0</v>
       </c>
       <c r="O110" s="2">
-        <v>172.0</v>
+        <v>175.0</v>
       </c>
       <c r="P110" s="2">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>724.0</v>
+        <v>745.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,13 +8207,13 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>724.0</v>
+        <v>745.0</v>
       </c>
       <c r="O111" s="2">
-        <v>309.0</v>
+        <v>327.0</v>
       </c>
       <c r="P111" s="2">
-        <v>414.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q111" s="2">
         <v>1.0</v>
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>497.0</v>
+        <v>534.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,22 +8278,22 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>497.0</v>
+        <v>534.0</v>
       </c>
       <c r="O112" s="2">
+        <v>273.0</v>
+      </c>
+      <c r="P112" s="2">
         <v>257.0</v>
-      </c>
-      <c r="P112" s="2">
-        <v>236.0</v>
       </c>
       <c r="Q112" s="2">
         <v>4.0</v>
       </c>
       <c r="R112" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="S112" s="2">
-        <v>31.0</v>
+        <v>39.0</v>
       </c>
       <c r="T112" s="2">
         <v>1.0</v>
@@ -8305,7 +8305,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>43.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>473.0</v>
+        <v>515.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,13 +8349,13 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>473.0</v>
+        <v>515.0</v>
       </c>
       <c r="O113" s="2">
-        <v>157.0</v>
+        <v>172.0</v>
       </c>
       <c r="P113" s="2">
-        <v>316.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q113" s="2">
         <v>0.0</v>
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>520.0</v>
+        <v>523.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,13 +8420,13 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>520.0</v>
+        <v>523.0</v>
       </c>
       <c r="O114" s="2">
-        <v>265.0</v>
+        <v>267.0</v>
       </c>
       <c r="P114" s="2">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>497.0</v>
+        <v>517.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>496.0</v>
+        <v>516.0</v>
       </c>
       <c r="O117" s="2">
-        <v>235.0</v>
+        <v>253.0</v>
       </c>
       <c r="P117" s="2">
-        <v>262.0</v>
+        <v>264.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8763,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>579.0</v>
+        <v>601.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8775,22 +8775,22 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>579.0</v>
+        <v>601.0</v>
       </c>
       <c r="O119" s="2">
-        <v>333.0</v>
+        <v>345.0</v>
       </c>
       <c r="P119" s="2">
-        <v>242.0</v>
+        <v>252.0</v>
       </c>
       <c r="Q119" s="2">
         <v>4.0</v>
       </c>
       <c r="R119" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="S119" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="T119" s="2">
         <v>0.0</v>
@@ -8802,7 +8802,7 @@
         <v>0.0</v>
       </c>
       <c r="W119" s="2">
-        <v>42.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -8976,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>510.0</v>
+        <v>516.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8988,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>506.0</v>
+        <v>512.0</v>
       </c>
       <c r="O122" s="2">
-        <v>275.0</v>
+        <v>280.0</v>
       </c>
       <c r="P122" s="2">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9189,7 +9189,7 @@
         <v>1432.0</v>
       </c>
       <c r="J125" s="2">
-        <v>1135.0</v>
+        <v>1141.0</v>
       </c>
       <c r="K125" s="2">
         <v>1.0</v>
@@ -9201,16 +9201,16 @@
         <v>0.0</v>
       </c>
       <c r="N125" s="2">
-        <v>1135.0</v>
+        <v>1141.0</v>
       </c>
       <c r="O125" s="2">
-        <v>519.0</v>
+        <v>522.0</v>
       </c>
       <c r="P125" s="2">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="Q125" s="2">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="R125" s="2">
         <v>0.0</v>
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>707.0</v>
+        <v>723.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,13 +9343,13 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>707.0</v>
+        <v>723.0</v>
       </c>
       <c r="O127" s="2">
-        <v>448.0</v>
+        <v>462.0</v>
       </c>
       <c r="P127" s="2">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
@@ -9364,13 +9364,13 @@
         <v>2.0</v>
       </c>
       <c r="U127" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>805.0</v>
+        <v>808.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,13 +9414,13 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>805.0</v>
+        <v>808.0</v>
       </c>
       <c r="O128" s="2">
-        <v>428.0</v>
+        <v>429.0</v>
       </c>
       <c r="P128" s="2">
-        <v>375.0</v>
+        <v>377.0</v>
       </c>
       <c r="Q128" s="2">
         <v>2.0</v>
@@ -9544,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>518.0</v>
+        <v>561.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9556,16 +9556,16 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>516.0</v>
+        <v>559.0</v>
       </c>
       <c r="O130" s="2">
-        <v>337.0</v>
+        <v>361.0</v>
       </c>
       <c r="P130" s="2">
-        <v>160.0</v>
+        <v>173.0</v>
       </c>
       <c r="Q130" s="2">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="R130" s="2">
         <v>6.0</v>
@@ -9615,7 +9615,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>491.0</v>
+        <v>495.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9627,13 +9627,13 @@
         <v>5.0</v>
       </c>
       <c r="N131" s="2">
-        <v>486.0</v>
+        <v>490.0</v>
       </c>
       <c r="O131" s="2">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="P131" s="2">
-        <v>213.0</v>
+        <v>216.0</v>
       </c>
       <c r="Q131" s="2">
         <v>11.0</v>
@@ -9757,7 +9757,7 @@
         <v>1330.0</v>
       </c>
       <c r="J133" s="2">
-        <v>674.0</v>
+        <v>682.0</v>
       </c>
       <c r="K133" s="2">
         <v>1.0</v>
@@ -9769,13 +9769,13 @@
         <v>0.0</v>
       </c>
       <c r="N133" s="2">
-        <v>674.0</v>
+        <v>682.0</v>
       </c>
       <c r="O133" s="2">
-        <v>351.0</v>
+        <v>356.0</v>
       </c>
       <c r="P133" s="2">
-        <v>312.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q133" s="2">
         <v>11.0</v>
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>693.0</v>
+        <v>710.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,13 +9911,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>692.0</v>
+        <v>709.0</v>
       </c>
       <c r="O135" s="2">
-        <v>338.0</v>
+        <v>344.0</v>
       </c>
       <c r="P135" s="2">
-        <v>273.0</v>
+        <v>284.0</v>
       </c>
       <c r="Q135" s="2">
         <v>82.0</v>
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>442.0</v>
+        <v>466.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,19 +10053,19 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>442.0</v>
+        <v>466.0</v>
       </c>
       <c r="O137" s="2">
-        <v>172.0</v>
+        <v>185.0</v>
       </c>
       <c r="P137" s="2">
-        <v>257.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q137" s="2">
         <v>13.0</v>
       </c>
       <c r="R137" s="2">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="S137" s="2">
         <v>6.0</v>
@@ -10080,7 +10080,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10136,7 +10136,7 @@
         <v>24.0</v>
       </c>
       <c r="R138" s="2">
-        <v>16.0</v>
+        <v>22.0</v>
       </c>
       <c r="S138" s="2">
         <v>3.0</v>
@@ -10151,7 +10151,7 @@
         <v>0.0</v>
       </c>
       <c r="W138" s="2">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>724.0</v>
+        <v>730.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,13 +10195,13 @@
         <v>1.0</v>
       </c>
       <c r="N139" s="2">
-        <v>723.0</v>
+        <v>729.0</v>
       </c>
       <c r="O139" s="2">
-        <v>431.0</v>
+        <v>435.0</v>
       </c>
       <c r="P139" s="2">
-        <v>272.0</v>
+        <v>274.0</v>
       </c>
       <c r="Q139" s="2">
         <v>21.0</v>
@@ -10254,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>601.0</v>
+        <v>605.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10266,10 +10266,10 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>601.0</v>
+        <v>605.0</v>
       </c>
       <c r="O140" s="2">
-        <v>294.0</v>
+        <v>298.0</v>
       </c>
       <c r="P140" s="2">
         <v>306.0</v>
@@ -10325,7 +10325,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>519.0</v>
+        <v>551.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10337,13 +10337,13 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>518.0</v>
+        <v>550.0</v>
       </c>
       <c r="O141" s="2">
-        <v>283.0</v>
+        <v>309.0</v>
       </c>
       <c r="P141" s="2">
-        <v>236.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q141" s="2">
         <v>0.0</v>
@@ -10396,7 +10396,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" s="2">
-        <v>833.0</v>
+        <v>868.0</v>
       </c>
       <c r="K142" s="2">
         <v>1.0</v>
@@ -10408,13 +10408,13 @@
         <v>0.0</v>
       </c>
       <c r="N142" s="2">
-        <v>833.0</v>
+        <v>868.0</v>
       </c>
       <c r="O142" s="2">
-        <v>449.0</v>
+        <v>477.0</v>
       </c>
       <c r="P142" s="2">
-        <v>384.0</v>
+        <v>391.0</v>
       </c>
       <c r="Q142" s="2">
         <v>0.0</v>
@@ -10467,7 +10467,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>504.0</v>
+        <v>536.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10479,13 +10479,13 @@
         <v>1.0</v>
       </c>
       <c r="N143" s="2">
-        <v>503.0</v>
+        <v>535.0</v>
       </c>
       <c r="O143" s="2">
-        <v>293.0</v>
+        <v>315.0</v>
       </c>
       <c r="P143" s="2">
-        <v>211.0</v>
+        <v>221.0</v>
       </c>
       <c r="Q143" s="2">
         <v>0.0</v>
@@ -10609,7 +10609,7 @@
         <v>1012.0</v>
       </c>
       <c r="J145" s="2">
-        <v>574.0</v>
+        <v>575.0</v>
       </c>
       <c r="K145" s="2">
         <v>1.0</v>
@@ -10621,13 +10621,13 @@
         <v>0.0</v>
       </c>
       <c r="N145" s="2">
-        <v>574.0</v>
+        <v>575.0</v>
       </c>
       <c r="O145" s="2">
         <v>231.0</v>
       </c>
       <c r="P145" s="2">
-        <v>324.0</v>
+        <v>325.0</v>
       </c>
       <c r="Q145" s="2">
         <v>19.0</v>
@@ -10822,7 +10822,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>566.0</v>
+        <v>600.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10834,13 +10834,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>566.0</v>
+        <v>600.0</v>
       </c>
       <c r="O148" s="2">
-        <v>194.0</v>
+        <v>222.0</v>
       </c>
       <c r="P148" s="2">
-        <v>372.0</v>
+        <v>378.0</v>
       </c>
       <c r="Q148" s="2">
         <v>0.0</v>
@@ -11106,7 +11106,7 @@
         <v>942.0</v>
       </c>
       <c r="J152" s="2">
-        <v>517.0</v>
+        <v>533.0</v>
       </c>
       <c r="K152" s="2">
         <v>1.0</v>
@@ -11118,19 +11118,19 @@
         <v>1.0</v>
       </c>
       <c r="N152" s="2">
-        <v>516.0</v>
+        <v>532.0</v>
       </c>
       <c r="O152" s="2">
-        <v>251.0</v>
+        <v>258.0</v>
       </c>
       <c r="P152" s="2">
-        <v>266.0</v>
+        <v>275.0</v>
       </c>
       <c r="Q152" s="2">
         <v>0.0</v>
       </c>
       <c r="R152" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="S152" s="2">
         <v>0.0</v>
@@ -11145,7 +11145,7 @@
         <v>0.0</v>
       </c>
       <c r="W152" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
@@ -11177,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>700.0</v>
+        <v>748.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11189,13 +11189,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>700.0</v>
+        <v>748.0</v>
       </c>
       <c r="O153" s="2">
-        <v>343.0</v>
+        <v>362.0</v>
       </c>
       <c r="P153" s="2">
-        <v>357.0</v>
+        <v>386.0</v>
       </c>
       <c r="Q153" s="2">
         <v>0.0</v>
@@ -11248,7 +11248,7 @@
         <v>999.0</v>
       </c>
       <c r="J154" s="2">
-        <v>545.0</v>
+        <v>546.0</v>
       </c>
       <c r="K154" s="2">
         <v>1.0</v>
@@ -11260,7 +11260,7 @@
         <v>0.0</v>
       </c>
       <c r="N154" s="2">
-        <v>545.0</v>
+        <v>546.0</v>
       </c>
       <c r="O154" s="2">
         <v>30.0</v>
@@ -11269,7 +11269,7 @@
         <v>307.0</v>
       </c>
       <c r="Q154" s="2">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="R154" s="2">
         <v>0.0</v>
@@ -11390,7 +11390,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="K156" s="2">
         <v>1.0</v>
@@ -11402,10 +11402,10 @@
         <v>0.0</v>
       </c>
       <c r="N156" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="O156" s="2">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="P156" s="2">
         <v>442.0</v>
@@ -11461,7 +11461,7 @@
         <v>1501.0</v>
       </c>
       <c r="J157" s="2">
-        <v>705.0</v>
+        <v>718.0</v>
       </c>
       <c r="K157" s="2">
         <v>1.0</v>
@@ -11473,13 +11473,13 @@
         <v>4.0</v>
       </c>
       <c r="N157" s="2">
-        <v>701.0</v>
+        <v>714.0</v>
       </c>
       <c r="O157" s="2">
-        <v>239.0</v>
+        <v>243.0</v>
       </c>
       <c r="P157" s="2">
-        <v>466.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q157" s="2">
         <v>0.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>690.0</v>
+        <v>713.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>689.0</v>
+        <v>712.0</v>
       </c>
       <c r="O159" s="2">
-        <v>387.0</v>
+        <v>403.0</v>
       </c>
       <c r="P159" s="2">
-        <v>303.0</v>
+        <v>310.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11674,7 +11674,7 @@
         <v>1283.0</v>
       </c>
       <c r="J160" s="2">
-        <v>789.0</v>
+        <v>790.0</v>
       </c>
       <c r="K160" s="2">
         <v>1.0</v>
@@ -11686,10 +11686,10 @@
         <v>0.0</v>
       </c>
       <c r="N160" s="2">
-        <v>789.0</v>
+        <v>790.0</v>
       </c>
       <c r="O160" s="2">
-        <v>392.0</v>
+        <v>393.0</v>
       </c>
       <c r="P160" s="2">
         <v>397.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>578.0</v>
+        <v>747.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,13 +11757,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>578.0</v>
+        <v>747.0</v>
       </c>
       <c r="O161" s="2">
-        <v>293.0</v>
+        <v>381.0</v>
       </c>
       <c r="P161" s="2">
-        <v>277.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>679.0</v>
+        <v>722.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>678.0</v>
+        <v>721.0</v>
       </c>
       <c r="O162" s="2">
         <v>13.0</v>
       </c>
       <c r="P162" s="2">
-        <v>171.0</v>
+        <v>177.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>495.0</v>
+        <v>532.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>659.0</v>
+        <v>665.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,16 +11899,16 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>659.0</v>
+        <v>665.0</v>
       </c>
       <c r="O163" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="P163" s="2">
-        <v>300.0</v>
+        <v>301.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>351.0</v>
+        <v>354.0</v>
       </c>
       <c r="R163" s="2">
         <v>0.0</v>
@@ -11958,7 +11958,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" s="2">
-        <v>670.0</v>
+        <v>675.0</v>
       </c>
       <c r="K164" s="2">
         <v>1.0</v>
@@ -11970,16 +11970,16 @@
         <v>1.0</v>
       </c>
       <c r="N164" s="2">
-        <v>669.0</v>
+        <v>674.0</v>
       </c>
       <c r="O164" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="P164" s="2">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q164" s="2">
-        <v>365.0</v>
+        <v>366.0</v>
       </c>
       <c r="R164" s="2">
         <v>0.0</v>
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>534.0</v>
+        <v>548.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,19 +12112,19 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>534.0</v>
+        <v>548.0</v>
       </c>
       <c r="O166" s="2">
-        <v>281.0</v>
+        <v>292.0</v>
       </c>
       <c r="P166" s="2">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
       </c>
       <c r="R166" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="S166" s="2">
         <v>0.0</v>
@@ -12139,7 +12139,7 @@
         <v>0.0</v>
       </c>
       <c r="W166" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -12171,7 +12171,7 @@
         <v>667.0</v>
       </c>
       <c r="J167" s="2">
-        <v>535.0</v>
+        <v>539.0</v>
       </c>
       <c r="K167" s="2">
         <v>1.0</v>
@@ -12183,13 +12183,13 @@
         <v>0.0</v>
       </c>
       <c r="N167" s="2">
-        <v>535.0</v>
+        <v>539.0</v>
       </c>
       <c r="O167" s="2">
-        <v>261.0</v>
+        <v>264.0</v>
       </c>
       <c r="P167" s="2">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="Q167" s="2">
         <v>0.0</v>
@@ -12201,7 +12201,7 @@
         <v>0.0</v>
       </c>
       <c r="T167" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U167" s="2">
         <v>0.0</v>
@@ -12210,7 +12210,7 @@
         <v>0.0</v>
       </c>
       <c r="W167" s="2">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
@@ -12242,7 +12242,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>505.0</v>
+        <v>516.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12254,13 +12254,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>505.0</v>
+        <v>516.0</v>
       </c>
       <c r="O168" s="2">
-        <v>148.0</v>
+        <v>153.0</v>
       </c>
       <c r="P168" s="2">
-        <v>269.0</v>
+        <v>275.0</v>
       </c>
       <c r="Q168" s="2">
         <v>88.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>360.0</v>
+        <v>371.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,13 +12325,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>360.0</v>
+        <v>371.0</v>
       </c>
       <c r="O169" s="2">
-        <v>153.0</v>
+        <v>163.0</v>
       </c>
       <c r="P169" s="2">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="Q169" s="2">
         <v>8.0</v>
@@ -12526,7 +12526,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>364.0</v>
+        <v>383.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12538,13 +12538,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>364.0</v>
+        <v>383.0</v>
       </c>
       <c r="O172" s="2">
-        <v>181.0</v>
+        <v>186.0</v>
       </c>
       <c r="P172" s="2">
-        <v>183.0</v>
+        <v>197.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
@@ -12668,7 +12668,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" s="2">
-        <v>870.0</v>
+        <v>881.0</v>
       </c>
       <c r="K174" s="2">
         <v>1.0</v>
@@ -12680,13 +12680,13 @@
         <v>0.0</v>
       </c>
       <c r="N174" s="2">
-        <v>870.0</v>
+        <v>881.0</v>
       </c>
       <c r="O174" s="2">
-        <v>431.0</v>
+        <v>440.0</v>
       </c>
       <c r="P174" s="2">
-        <v>439.0</v>
+        <v>441.0</v>
       </c>
       <c r="Q174" s="2">
         <v>0.0</v>
@@ -12739,7 +12739,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" s="2">
-        <v>809.0</v>
+        <v>875.0</v>
       </c>
       <c r="K175" s="2">
         <v>1.0</v>
@@ -12751,13 +12751,13 @@
         <v>0.0</v>
       </c>
       <c r="N175" s="2">
-        <v>809.0</v>
+        <v>875.0</v>
       </c>
       <c r="O175" s="2">
-        <v>379.0</v>
+        <v>414.0</v>
       </c>
       <c r="P175" s="2">
-        <v>430.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q175" s="2">
         <v>0.0</v>
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>340.0</v>
+        <v>373.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,19 +12893,19 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>340.0</v>
+        <v>373.0</v>
       </c>
       <c r="O177" s="2">
-        <v>147.0</v>
+        <v>172.0</v>
       </c>
       <c r="P177" s="2">
-        <v>193.0</v>
+        <v>201.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
       </c>
       <c r="R177" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S177" s="2">
         <v>22.0</v>
@@ -12920,7 +12920,7 @@
         <v>0.0</v>
       </c>
       <c r="W177" s="2">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>528.0</v>
+        <v>540.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,13 +13035,13 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>528.0</v>
+        <v>540.0</v>
       </c>
       <c r="O179" s="2">
-        <v>320.0</v>
+        <v>328.0</v>
       </c>
       <c r="P179" s="2">
-        <v>207.0</v>
+        <v>211.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
@@ -13094,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>351.0</v>
+        <v>354.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13106,10 +13106,10 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>351.0</v>
+        <v>354.0</v>
       </c>
       <c r="O180" s="2">
-        <v>180.0</v>
+        <v>183.0</v>
       </c>
       <c r="P180" s="2">
         <v>171.0</v>
@@ -13118,10 +13118,10 @@
         <v>0.0</v>
       </c>
       <c r="R180" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S180" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="T180" s="2">
         <v>0.0</v>
@@ -13133,7 +13133,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" s="2">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -13192,19 +13192,19 @@
         <v>5.0</v>
       </c>
       <c r="S181" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="T181" s="2">
         <v>0.0</v>
       </c>
       <c r="U181" s="2">
-        <v>14.0</v>
+        <v>52.0</v>
       </c>
       <c r="V181" s="2">
         <v>0.0</v>
       </c>
       <c r="W181" s="2">
-        <v>20.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -13236,7 +13236,7 @@
         <v>753.0</v>
       </c>
       <c r="J182" s="2">
-        <v>544.0</v>
+        <v>553.0</v>
       </c>
       <c r="K182" s="2">
         <v>1.0</v>
@@ -13248,13 +13248,13 @@
         <v>0.0</v>
       </c>
       <c r="N182" s="2">
-        <v>544.0</v>
+        <v>553.0</v>
       </c>
       <c r="O182" s="2">
-        <v>242.0</v>
+        <v>248.0</v>
       </c>
       <c r="P182" s="2">
-        <v>301.0</v>
+        <v>304.0</v>
       </c>
       <c r="Q182" s="2">
         <v>1.0</v>
@@ -13307,7 +13307,7 @@
         <v>996.0</v>
       </c>
       <c r="J183" s="2">
-        <v>882.0</v>
+        <v>899.0</v>
       </c>
       <c r="K183" s="2">
         <v>1.0</v>
@@ -13319,13 +13319,13 @@
         <v>0.0</v>
       </c>
       <c r="N183" s="2">
-        <v>882.0</v>
+        <v>899.0</v>
       </c>
       <c r="O183" s="2">
-        <v>411.0</v>
+        <v>416.0</v>
       </c>
       <c r="P183" s="2">
-        <v>471.0</v>
+        <v>483.0</v>
       </c>
       <c r="Q183" s="2">
         <v>0.0</v>
@@ -13378,7 +13378,7 @@
         <v>899.0</v>
       </c>
       <c r="J184" s="2">
-        <v>323.0</v>
+        <v>338.0</v>
       </c>
       <c r="K184" s="2">
         <v>1.0</v>
@@ -13390,13 +13390,13 @@
         <v>1.0</v>
       </c>
       <c r="N184" s="2">
-        <v>322.0</v>
+        <v>337.0</v>
       </c>
       <c r="O184" s="2">
-        <v>155.0</v>
+        <v>163.0</v>
       </c>
       <c r="P184" s="2">
-        <v>167.0</v>
+        <v>174.0</v>
       </c>
       <c r="Q184" s="2">
         <v>1.0</v>
@@ -13449,7 +13449,7 @@
         <v>1000.0</v>
       </c>
       <c r="J185" s="2">
-        <v>577.0</v>
+        <v>639.0</v>
       </c>
       <c r="K185" s="2">
         <v>1.0</v>
@@ -13461,13 +13461,13 @@
         <v>0.0</v>
       </c>
       <c r="N185" s="2">
-        <v>577.0</v>
+        <v>639.0</v>
       </c>
       <c r="O185" s="2">
-        <v>292.0</v>
+        <v>331.0</v>
       </c>
       <c r="P185" s="2">
-        <v>285.0</v>
+        <v>308.0</v>
       </c>
       <c r="Q185" s="2">
         <v>0.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>597.0</v>
+        <v>616.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,16 +13532,16 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>597.0</v>
+        <v>616.0</v>
       </c>
       <c r="O186" s="2">
         <v>118.0</v>
       </c>
       <c r="P186" s="2">
-        <v>277.0</v>
+        <v>283.0</v>
       </c>
       <c r="Q186" s="2">
-        <v>202.0</v>
+        <v>215.0</v>
       </c>
       <c r="R186" s="2">
         <v>1.0</v>
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>546.0</v>
+        <v>557.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,13 +13674,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>546.0</v>
+        <v>557.0</v>
       </c>
       <c r="O188" s="2">
-        <v>162.0</v>
+        <v>165.0</v>
       </c>
       <c r="P188" s="2">
-        <v>326.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q188" s="2">
         <v>58.0</v>
@@ -13804,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>683.0</v>
+        <v>745.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13816,22 +13816,22 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>683.0</v>
+        <v>745.0</v>
       </c>
       <c r="O190" s="2">
-        <v>340.0</v>
+        <v>386.0</v>
       </c>
       <c r="P190" s="2">
-        <v>322.0</v>
+        <v>338.0</v>
       </c>
       <c r="Q190" s="2">
         <v>21.0</v>
       </c>
       <c r="R190" s="2">
-        <v>18.0</v>
+        <v>37.0</v>
       </c>
       <c r="S190" s="2">
-        <v>27.0</v>
+        <v>47.0</v>
       </c>
       <c r="T190" s="2">
         <v>2.0</v>
@@ -13843,7 +13843,7 @@
         <v>0.0</v>
       </c>
       <c r="W190" s="2">
-        <v>48.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -13875,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>546.0</v>
+        <v>585.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13887,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>546.0</v>
+        <v>585.0</v>
       </c>
       <c r="O191" s="2">
-        <v>224.0</v>
+        <v>262.0</v>
       </c>
       <c r="P191" s="2">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -13946,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13958,13 +13958,13 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="O192" s="2">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="P192" s="2">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="Q192" s="2">
         <v>2.0</v>
@@ -14017,7 +14017,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>864.0</v>
+        <v>973.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14029,16 +14029,16 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>864.0</v>
+        <v>973.0</v>
       </c>
       <c r="O193" s="2">
-        <v>288.0</v>
+        <v>332.0</v>
       </c>
       <c r="P193" s="2">
-        <v>407.0</v>
+        <v>441.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>169.0</v>
+        <v>200.0</v>
       </c>
       <c r="R193" s="2">
         <v>0.0</v>
@@ -14088,7 +14088,7 @@
         <v>452.0</v>
       </c>
       <c r="J194" s="2">
-        <v>237.0</v>
+        <v>271.0</v>
       </c>
       <c r="K194" s="2">
         <v>1.0</v>
@@ -14100,16 +14100,16 @@
         <v>0.0</v>
       </c>
       <c r="N194" s="2">
-        <v>237.0</v>
+        <v>271.0</v>
       </c>
       <c r="O194" s="2">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="P194" s="2">
-        <v>149.0</v>
+        <v>168.0</v>
       </c>
       <c r="Q194" s="2">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
       <c r="R194" s="2">
         <v>0.0</v>
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,16 +14171,16 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="O195" s="2">
         <v>71.0</v>
       </c>
       <c r="P195" s="2">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
       <c r="R195" s="2">
         <v>0.0</v>
@@ -14230,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1089.0</v>
+        <v>1105.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14242,13 +14242,13 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1089.0</v>
+        <v>1105.0</v>
       </c>
       <c r="O196" s="2">
-        <v>425.0</v>
+        <v>431.0</v>
       </c>
       <c r="P196" s="2">
-        <v>478.0</v>
+        <v>488.0</v>
       </c>
       <c r="Q196" s="2">
         <v>186.0</v>
@@ -14301,7 +14301,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" s="2">
-        <v>1058.0</v>
+        <v>1059.0</v>
       </c>
       <c r="K197" s="2">
         <v>1.0</v>
@@ -14313,10 +14313,10 @@
         <v>0.0</v>
       </c>
       <c r="N197" s="2">
-        <v>1058.0</v>
+        <v>1059.0</v>
       </c>
       <c r="O197" s="2">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="P197" s="2">
         <v>348.0</v>
@@ -14325,7 +14325,7 @@
         <v>118.0</v>
       </c>
       <c r="R197" s="2">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="S197" s="2">
         <v>0.0</v>
@@ -14340,7 +14340,7 @@
         <v>0.0</v>
       </c>
       <c r="W197" s="2">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
@@ -14372,7 +14372,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" s="2">
-        <v>1122.0</v>
+        <v>1161.0</v>
       </c>
       <c r="K198" s="2">
         <v>1.0</v>
@@ -14384,25 +14384,25 @@
         <v>0.0</v>
       </c>
       <c r="N198" s="2">
-        <v>1122.0</v>
+        <v>1161.0</v>
       </c>
       <c r="O198" s="2">
-        <v>312.0</v>
+        <v>319.0</v>
       </c>
       <c r="P198" s="2">
-        <v>549.0</v>
+        <v>567.0</v>
       </c>
       <c r="Q198" s="2">
-        <v>261.0</v>
+        <v>275.0</v>
       </c>
       <c r="R198" s="2">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="S198" s="2">
         <v>1.0</v>
       </c>
       <c r="T198" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="U198" s="2">
         <v>0.0</v>
@@ -14411,7 +14411,7 @@
         <v>0.0</v>
       </c>
       <c r="W198" s="2">
-        <v>1.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>471.0</v>
+        <v>480.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,22 +14526,22 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>471.0</v>
+        <v>480.0</v>
       </c>
       <c r="O200" s="2">
-        <v>289.0</v>
+        <v>297.0</v>
       </c>
       <c r="P200" s="2">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
       </c>
       <c r="R200" s="2">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="S200" s="2">
-        <v>10.0</v>
+        <v>26.0</v>
       </c>
       <c r="T200" s="2">
         <v>1.0</v>
@@ -14553,7 +14553,7 @@
         <v>0.0</v>
       </c>
       <c r="W200" s="2">
-        <v>14.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14585,7 +14585,7 @@
         <v>1283.0</v>
       </c>
       <c r="J201" s="2">
-        <v>661.0</v>
+        <v>712.0</v>
       </c>
       <c r="K201" s="2">
         <v>1.0</v>
@@ -14597,16 +14597,16 @@
         <v>0.0</v>
       </c>
       <c r="N201" s="2">
-        <v>661.0</v>
+        <v>712.0</v>
       </c>
       <c r="O201" s="2">
-        <v>342.0</v>
+        <v>371.0</v>
       </c>
       <c r="P201" s="2">
-        <v>315.0</v>
+        <v>333.0</v>
       </c>
       <c r="Q201" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="R201" s="2">
         <v>22.0</v>
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>350.0</v>
+        <v>374.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>350.0</v>
+        <v>374.0</v>
       </c>
       <c r="O202" s="2">
-        <v>189.0</v>
+        <v>207.0</v>
       </c>
       <c r="P202" s="2">
-        <v>161.0</v>
+        <v>167.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14798,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>405.0</v>
+        <v>429.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14810,19 +14810,19 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>405.0</v>
+        <v>429.0</v>
       </c>
       <c r="O204" s="2">
-        <v>216.0</v>
+        <v>231.0</v>
       </c>
       <c r="P204" s="2">
-        <v>183.0</v>
+        <v>192.0</v>
       </c>
       <c r="Q204" s="2">
         <v>6.0</v>
       </c>
       <c r="R204" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="S204" s="2">
         <v>0.0</v>
@@ -14837,7 +14837,7 @@
         <v>0.0</v>
       </c>
       <c r="W204" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>330.0</v>
+        <v>364.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,13 +14881,13 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>330.0</v>
+        <v>364.0</v>
       </c>
       <c r="O205" s="2">
-        <v>148.0</v>
+        <v>170.0</v>
       </c>
       <c r="P205" s="2">
-        <v>154.0</v>
+        <v>166.0</v>
       </c>
       <c r="Q205" s="2">
         <v>28.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>620.0</v>
+        <v>633.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,19 +14952,19 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>620.0</v>
+        <v>633.0</v>
       </c>
       <c r="O206" s="2">
-        <v>364.0</v>
+        <v>375.0</v>
       </c>
       <c r="P206" s="2">
-        <v>256.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
       </c>
       <c r="R206" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="S206" s="2">
         <v>3.0</v>
@@ -14979,7 +14979,7 @@
         <v>0.0</v>
       </c>
       <c r="W206" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="207" ht="15.75" customHeight="1">
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>414.0</v>
+        <v>425.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>414.0</v>
+        <v>425.0</v>
       </c>
       <c r="O207" s="2">
-        <v>236.0</v>
+        <v>241.0</v>
       </c>
       <c r="P207" s="2">
-        <v>174.0</v>
+        <v>180.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
@@ -15082,7 +15082,7 @@
         <v>762.0</v>
       </c>
       <c r="J208" s="2">
-        <v>465.0</v>
+        <v>487.0</v>
       </c>
       <c r="K208" s="2">
         <v>1.0</v>
@@ -15094,16 +15094,16 @@
         <v>0.0</v>
       </c>
       <c r="N208" s="2">
-        <v>465.0</v>
+        <v>487.0</v>
       </c>
       <c r="O208" s="2">
         <v>123.0</v>
       </c>
       <c r="P208" s="2">
-        <v>205.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q208" s="2">
-        <v>137.0</v>
+        <v>149.0</v>
       </c>
       <c r="R208" s="2">
         <v>0.0</v>
@@ -15153,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>735.0</v>
+        <v>745.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15165,13 +15165,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>735.0</v>
+        <v>745.0</v>
       </c>
       <c r="O209" s="2">
-        <v>356.0</v>
+        <v>364.0</v>
       </c>
       <c r="P209" s="2">
-        <v>379.0</v>
+        <v>381.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15224,7 +15224,7 @@
         <v>792.0</v>
       </c>
       <c r="J210" s="2">
-        <v>573.0</v>
+        <v>574.0</v>
       </c>
       <c r="K210" s="2">
         <v>1.0</v>
@@ -15236,10 +15236,10 @@
         <v>0.0</v>
       </c>
       <c r="N210" s="2">
-        <v>573.0</v>
+        <v>574.0</v>
       </c>
       <c r="O210" s="2">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="P210" s="2">
         <v>301.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>562.0</v>
+        <v>576.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>562.0</v>
+        <v>576.0</v>
       </c>
       <c r="O213" s="2">
-        <v>293.0</v>
+        <v>299.0</v>
       </c>
       <c r="P213" s="2">
-        <v>269.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>620.0</v>
+        <v>661.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,19 +15591,19 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>620.0</v>
+        <v>661.0</v>
       </c>
       <c r="O215" s="2">
-        <v>232.0</v>
+        <v>264.0</v>
       </c>
       <c r="P215" s="2">
-        <v>388.0</v>
+        <v>397.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
       </c>
       <c r="R215" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="S215" s="2">
         <v>8.0</v>
@@ -15618,7 +15618,7 @@
         <v>0.0</v>
       </c>
       <c r="W215" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
@@ -15721,7 +15721,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>563.0</v>
+        <v>577.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15733,13 +15733,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>563.0</v>
+        <v>577.0</v>
       </c>
       <c r="O217" s="2">
-        <v>244.0</v>
+        <v>251.0</v>
       </c>
       <c r="P217" s="2">
-        <v>319.0</v>
+        <v>326.0</v>
       </c>
       <c r="Q217" s="2">
         <v>0.0</v>
@@ -15792,7 +15792,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>476.0</v>
+        <v>535.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15804,19 +15804,19 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>475.0</v>
+        <v>534.0</v>
       </c>
       <c r="O218" s="2">
-        <v>255.0</v>
+        <v>281.0</v>
       </c>
       <c r="P218" s="2">
-        <v>221.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="S218" s="2">
         <v>1.0</v>
@@ -15831,7 +15831,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>673.0</v>
+        <v>789.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,22 +15875,22 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>673.0</v>
+        <v>789.0</v>
       </c>
       <c r="O219" s="2">
         <v>102.0</v>
       </c>
       <c r="P219" s="2">
-        <v>294.0</v>
+        <v>337.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>277.0</v>
+        <v>350.0</v>
       </c>
       <c r="R219" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S219" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="T219" s="2">
         <v>2.0</v>
@@ -15902,7 +15902,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -16005,7 +16005,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>507.0</v>
+        <v>538.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16017,7 +16017,7 @@
         <v>1.0</v>
       </c>
       <c r="N221" s="2">
-        <v>506.0</v>
+        <v>537.0</v>
       </c>
       <c r="O221" s="2">
         <v>115.0</v>
@@ -16026,10 +16026,10 @@
         <v>230.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>162.0</v>
+        <v>193.0</v>
       </c>
       <c r="R221" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S221" s="2">
         <v>0.0</v>
@@ -16044,7 +16044,7 @@
         <v>0.0</v>
       </c>
       <c r="W221" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>565.0</v>
+        <v>613.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,16 +16088,16 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>565.0</v>
+        <v>613.0</v>
       </c>
       <c r="O222" s="2">
         <v>126.0</v>
       </c>
       <c r="P222" s="2">
-        <v>242.0</v>
+        <v>266.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>197.0</v>
+        <v>221.0</v>
       </c>
       <c r="R222" s="2">
         <v>0.0</v>
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>678.0</v>
+        <v>700.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,7 +16159,7 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>678.0</v>
+        <v>700.0</v>
       </c>
       <c r="O223" s="2">
         <v>66.0</v>
@@ -16168,7 +16168,7 @@
         <v>243.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>369.0</v>
+        <v>391.0</v>
       </c>
       <c r="R223" s="2">
         <v>0.0</v>
@@ -16218,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>430.0</v>
+        <v>438.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16230,7 +16230,7 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>430.0</v>
+        <v>438.0</v>
       </c>
       <c r="O224" s="2">
         <v>19.0</v>
@@ -16239,7 +16239,7 @@
         <v>33.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>378.0</v>
+        <v>386.0</v>
       </c>
       <c r="R224" s="2">
         <v>1.0</v>
@@ -16289,7 +16289,7 @@
         <v>1423.0</v>
       </c>
       <c r="J225" s="2">
-        <v>1234.0</v>
+        <v>1249.0</v>
       </c>
       <c r="K225" s="2">
         <v>1.0</v>
@@ -16301,13 +16301,13 @@
         <v>0.0</v>
       </c>
       <c r="N225" s="2">
-        <v>1234.0</v>
+        <v>1249.0</v>
       </c>
       <c r="O225" s="2">
-        <v>701.0</v>
+        <v>712.0</v>
       </c>
       <c r="P225" s="2">
-        <v>533.0</v>
+        <v>537.0</v>
       </c>
       <c r="Q225" s="2">
         <v>0.0</v>
@@ -16384,10 +16384,10 @@
         <v>275.0</v>
       </c>
       <c r="R226" s="2">
-        <v>30.0</v>
+        <v>77.0</v>
       </c>
       <c r="S226" s="2">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="T226" s="2">
         <v>0.0</v>
@@ -16399,7 +16399,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>44.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16644,7 +16644,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>457.0</v>
+        <v>496.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16656,16 +16656,16 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>457.0</v>
+        <v>496.0</v>
       </c>
       <c r="O230" s="2">
-        <v>69.0</v>
+        <v>80.0</v>
       </c>
       <c r="P230" s="2">
-        <v>211.0</v>
+        <v>226.0</v>
       </c>
       <c r="Q230" s="2">
-        <v>177.0</v>
+        <v>190.0</v>
       </c>
       <c r="R230" s="2">
         <v>0.0</v>
@@ -16715,7 +16715,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16727,10 +16727,10 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
       <c r="O231" s="2">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="P231" s="2">
         <v>299.0</v>
@@ -16742,7 +16742,7 @@
         <v>10.0</v>
       </c>
       <c r="S231" s="2">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T231" s="2">
         <v>1.0</v>
@@ -16754,7 +16754,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>501.0</v>
+        <v>527.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,16 +16798,16 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>501.0</v>
+        <v>527.0</v>
       </c>
       <c r="O232" s="2">
         <v>5.0</v>
       </c>
       <c r="P232" s="2">
-        <v>72.0</v>
+        <v>84.0</v>
       </c>
       <c r="Q232" s="2">
-        <v>424.0</v>
+        <v>438.0</v>
       </c>
       <c r="R232" s="2">
         <v>1.0</v>
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,13 +16869,13 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
       <c r="O233" s="2">
         <v>81.0</v>
       </c>
       <c r="P233" s="2">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="Q233" s="2">
         <v>130.0</v>
